--- a/accord/data/hotel_sales_data.xlsx
+++ b/accord/data/hotel_sales_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BL127"/>
+  <dimension ref="A1:BT127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -749,6 +749,46 @@
           <t>pct_sous_cat_souvenirs_nombre_produits</t>
         </is>
       </c>
+      <c r="BM1" s="1" t="inlineStr">
+        <is>
+          <t>nombre_ventes_holidays</t>
+        </is>
+      </c>
+      <c r="BN1" s="1" t="inlineStr">
+        <is>
+          <t>montant_ventes_holidays</t>
+        </is>
+      </c>
+      <c r="BO1" s="1" t="inlineStr">
+        <is>
+          <t>nombre_ventes_hors_holidays</t>
+        </is>
+      </c>
+      <c r="BP1" s="1" t="inlineStr">
+        <is>
+          <t>montant_ventes_hors_holidays</t>
+        </is>
+      </c>
+      <c r="BQ1" s="1" t="inlineStr">
+        <is>
+          <t>pct_nombre_ventes_holidays</t>
+        </is>
+      </c>
+      <c r="BR1" s="1" t="inlineStr">
+        <is>
+          <t>pct_montant_ventes_holidays</t>
+        </is>
+      </c>
+      <c r="BS1" s="1" t="inlineStr">
+        <is>
+          <t>pct_nombre_ventes_hors_holidays</t>
+        </is>
+      </c>
+      <c r="BT1" s="1" t="inlineStr">
+        <is>
+          <t>pct_montant_ventes_hors_holidays</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -947,6 +987,30 @@
       <c r="BL2" t="n">
         <v>0</v>
       </c>
+      <c r="BM2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO2" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BQ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS2" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1145,6 +1209,30 @@
       <c r="BL3" t="n">
         <v>0</v>
       </c>
+      <c r="BM3" t="n">
+        <v>167</v>
+      </c>
+      <c r="BN3" t="n">
+        <v>1508</v>
+      </c>
+      <c r="BO3" t="n">
+        <v>209</v>
+      </c>
+      <c r="BP3" t="n">
+        <v>1474.5</v>
+      </c>
+      <c r="BQ3" t="n">
+        <v>0.4441489361702128</v>
+      </c>
+      <c r="BR3" t="n">
+        <v>0.5056160938809723</v>
+      </c>
+      <c r="BS3" t="n">
+        <v>0.5558510638297872</v>
+      </c>
+      <c r="BT3" t="n">
+        <v>0.4943839061190277</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1343,6 +1431,30 @@
       <c r="BL4" t="n">
         <v>0.1</v>
       </c>
+      <c r="BM4" t="n">
+        <v>345</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>2171.5</v>
+      </c>
+      <c r="BO4" t="n">
+        <v>303</v>
+      </c>
+      <c r="BP4" t="n">
+        <v>2128.5</v>
+      </c>
+      <c r="BQ4" t="n">
+        <v>0.5324074074074074</v>
+      </c>
+      <c r="BR4" t="n">
+        <v>0.505</v>
+      </c>
+      <c r="BS4" t="n">
+        <v>0.4675925925925926</v>
+      </c>
+      <c r="BT4" t="n">
+        <v>0.495</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1541,6 +1653,30 @@
       <c r="BL5" t="n">
         <v>0.1083333333333333</v>
       </c>
+      <c r="BM5" t="n">
+        <v>423</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>3015</v>
+      </c>
+      <c r="BO5" t="n">
+        <v>323</v>
+      </c>
+      <c r="BP5" t="n">
+        <v>2516</v>
+      </c>
+      <c r="BQ5" t="n">
+        <v>0.5670241286863271</v>
+      </c>
+      <c r="BR5" t="n">
+        <v>0.5451093834749593</v>
+      </c>
+      <c r="BS5" t="n">
+        <v>0.4329758713136729</v>
+      </c>
+      <c r="BT5" t="n">
+        <v>0.4548906165250407</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1739,6 +1875,30 @@
       <c r="BL6" t="n">
         <v>0.08333333333333333</v>
       </c>
+      <c r="BM6" t="n">
+        <v>318</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>2573</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>318</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>2257</v>
+      </c>
+      <c r="BQ6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BR6" t="n">
+        <v>0.532712215320911</v>
+      </c>
+      <c r="BS6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BT6" t="n">
+        <v>0.467287784679089</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1937,6 +2097,30 @@
       <c r="BL7" t="n">
         <v>0.2844827586206897</v>
       </c>
+      <c r="BM7" t="n">
+        <v>203</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>1331</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>603</v>
+      </c>
+      <c r="BP7" t="n">
+        <v>4603</v>
+      </c>
+      <c r="BQ7" t="n">
+        <v>0.2518610421836228</v>
+      </c>
+      <c r="BR7" t="n">
+        <v>0.2243006403774857</v>
+      </c>
+      <c r="BS7" t="n">
+        <v>0.7481389578163772</v>
+      </c>
+      <c r="BT7" t="n">
+        <v>0.7756993596225144</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2135,6 +2319,30 @@
       <c r="BL8" t="n">
         <v>0.287037037037037</v>
       </c>
+      <c r="BM8" t="n">
+        <v>479</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>3452</v>
+      </c>
+      <c r="BO8" t="n">
+        <v>138</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>1041</v>
+      </c>
+      <c r="BQ8" t="n">
+        <v>0.7763371150729336</v>
+      </c>
+      <c r="BR8" t="n">
+        <v>0.7683062541731582</v>
+      </c>
+      <c r="BS8" t="n">
+        <v>0.2236628849270665</v>
+      </c>
+      <c r="BT8" t="n">
+        <v>0.2316937458268417</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2333,6 +2541,30 @@
       <c r="BL9" t="n">
         <v>0.3333333333333333</v>
       </c>
+      <c r="BM9" t="n">
+        <v>615</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>5143</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ9" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR9" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2531,6 +2763,30 @@
       <c r="BL10" t="n">
         <v>0.3333333333333333</v>
       </c>
+      <c r="BM10" t="n">
+        <v>296</v>
+      </c>
+      <c r="BN10" t="n">
+        <v>2586</v>
+      </c>
+      <c r="BO10" t="n">
+        <v>605</v>
+      </c>
+      <c r="BP10" t="n">
+        <v>5286</v>
+      </c>
+      <c r="BQ10" t="n">
+        <v>0.3285238623751388</v>
+      </c>
+      <c r="BR10" t="n">
+        <v>0.3285060975609756</v>
+      </c>
+      <c r="BS10" t="n">
+        <v>0.6714761376248612</v>
+      </c>
+      <c r="BT10" t="n">
+        <v>0.6714939024390244</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2729,6 +2985,30 @@
       <c r="BL11" t="n">
         <v>0.25</v>
       </c>
+      <c r="BM11" t="n">
+        <v>598</v>
+      </c>
+      <c r="BN11" t="n">
+        <v>5626</v>
+      </c>
+      <c r="BO11" t="n">
+        <v>443</v>
+      </c>
+      <c r="BP11" t="n">
+        <v>3543</v>
+      </c>
+      <c r="BQ11" t="n">
+        <v>0.574447646493756</v>
+      </c>
+      <c r="BR11" t="n">
+        <v>0.6135892681862799</v>
+      </c>
+      <c r="BS11" t="n">
+        <v>0.425552353506244</v>
+      </c>
+      <c r="BT11" t="n">
+        <v>0.3864107318137202</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2927,6 +3207,30 @@
       <c r="BL12" t="n">
         <v>0.04347826086956522</v>
       </c>
+      <c r="BM12" t="n">
+        <v>286</v>
+      </c>
+      <c r="BN12" t="n">
+        <v>2409</v>
+      </c>
+      <c r="BO12" t="n">
+        <v>420</v>
+      </c>
+      <c r="BP12" t="n">
+        <v>3177</v>
+      </c>
+      <c r="BQ12" t="n">
+        <v>0.405099150141643</v>
+      </c>
+      <c r="BR12" t="n">
+        <v>0.4312567132116004</v>
+      </c>
+      <c r="BS12" t="n">
+        <v>0.5949008498583569</v>
+      </c>
+      <c r="BT12" t="n">
+        <v>0.5687432867883996</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -3125,6 +3429,30 @@
       <c r="BL13" t="n">
         <v>0</v>
       </c>
+      <c r="BM13" t="n">
+        <v>351</v>
+      </c>
+      <c r="BN13" t="n">
+        <v>3265</v>
+      </c>
+      <c r="BO13" t="n">
+        <v>257</v>
+      </c>
+      <c r="BP13" t="n">
+        <v>2037</v>
+      </c>
+      <c r="BQ13" t="n">
+        <v>0.5773026315789473</v>
+      </c>
+      <c r="BR13" t="n">
+        <v>0.6158053564692569</v>
+      </c>
+      <c r="BS13" t="n">
+        <v>0.4226973684210527</v>
+      </c>
+      <c r="BT13" t="n">
+        <v>0.3841946435307431</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -3323,6 +3651,30 @@
       <c r="BL14" t="n">
         <v>0.08695652173913043</v>
       </c>
+      <c r="BM14" t="n">
+        <v>307</v>
+      </c>
+      <c r="BN14" t="n">
+        <v>2459</v>
+      </c>
+      <c r="BO14" t="n">
+        <v>285</v>
+      </c>
+      <c r="BP14" t="n">
+        <v>2474</v>
+      </c>
+      <c r="BQ14" t="n">
+        <v>0.518581081081081</v>
+      </c>
+      <c r="BR14" t="n">
+        <v>0.4984796270018245</v>
+      </c>
+      <c r="BS14" t="n">
+        <v>0.4814189189189189</v>
+      </c>
+      <c r="BT14" t="n">
+        <v>0.5015203729981755</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -3521,6 +3873,30 @@
       <c r="BL15" t="n">
         <v>0.4869565217391305</v>
       </c>
+      <c r="BM15" t="n">
+        <v>285</v>
+      </c>
+      <c r="BN15" t="n">
+        <v>2244</v>
+      </c>
+      <c r="BO15" t="n">
+        <v>217</v>
+      </c>
+      <c r="BP15" t="n">
+        <v>1776</v>
+      </c>
+      <c r="BQ15" t="n">
+        <v>0.5677290836653387</v>
+      </c>
+      <c r="BR15" t="n">
+        <v>0.5582089552238806</v>
+      </c>
+      <c r="BS15" t="n">
+        <v>0.4322709163346614</v>
+      </c>
+      <c r="BT15" t="n">
+        <v>0.4417910447761194</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -3719,6 +4095,30 @@
       <c r="BL16" t="n">
         <v>0.04761904761904762</v>
       </c>
+      <c r="BM16" t="n">
+        <v>288</v>
+      </c>
+      <c r="BN16" t="n">
+        <v>2210</v>
+      </c>
+      <c r="BO16" t="n">
+        <v>268</v>
+      </c>
+      <c r="BP16" t="n">
+        <v>1951</v>
+      </c>
+      <c r="BQ16" t="n">
+        <v>0.5179856115107914</v>
+      </c>
+      <c r="BR16" t="n">
+        <v>0.5311223263638548</v>
+      </c>
+      <c r="BS16" t="n">
+        <v>0.4820143884892086</v>
+      </c>
+      <c r="BT16" t="n">
+        <v>0.4688776736361451</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -3917,6 +4317,30 @@
       <c r="BL17" t="n">
         <v>0</v>
       </c>
+      <c r="BM17" t="n">
+        <v>240</v>
+      </c>
+      <c r="BN17" t="n">
+        <v>1982</v>
+      </c>
+      <c r="BO17" t="n">
+        <v>268</v>
+      </c>
+      <c r="BP17" t="n">
+        <v>2468</v>
+      </c>
+      <c r="BQ17" t="n">
+        <v>0.4724409448818898</v>
+      </c>
+      <c r="BR17" t="n">
+        <v>0.4453932584269663</v>
+      </c>
+      <c r="BS17" t="n">
+        <v>0.5275590551181102</v>
+      </c>
+      <c r="BT17" t="n">
+        <v>0.5546067415730337</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -4115,6 +4539,30 @@
       <c r="BL18" t="n">
         <v>0</v>
       </c>
+      <c r="BM18" t="n">
+        <v>165</v>
+      </c>
+      <c r="BN18" t="n">
+        <v>1338</v>
+      </c>
+      <c r="BO18" t="n">
+        <v>187</v>
+      </c>
+      <c r="BP18" t="n">
+        <v>1749</v>
+      </c>
+      <c r="BQ18" t="n">
+        <v>0.46875</v>
+      </c>
+      <c r="BR18" t="n">
+        <v>0.4334305150631681</v>
+      </c>
+      <c r="BS18" t="n">
+        <v>0.53125</v>
+      </c>
+      <c r="BT18" t="n">
+        <v>0.5665694849368319</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -4313,6 +4761,30 @@
       <c r="BL19" t="n">
         <v>0</v>
       </c>
+      <c r="BM19" t="n">
+        <v>153</v>
+      </c>
+      <c r="BN19" t="n">
+        <v>1068</v>
+      </c>
+      <c r="BO19" t="n">
+        <v>309</v>
+      </c>
+      <c r="BP19" t="n">
+        <v>2097</v>
+      </c>
+      <c r="BQ19" t="n">
+        <v>0.3311688311688312</v>
+      </c>
+      <c r="BR19" t="n">
+        <v>0.3374407582938388</v>
+      </c>
+      <c r="BS19" t="n">
+        <v>0.6688311688311688</v>
+      </c>
+      <c r="BT19" t="n">
+        <v>0.6625592417061611</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -4511,6 +4983,30 @@
       <c r="BL20" t="n">
         <v>0.25</v>
       </c>
+      <c r="BM20" t="n">
+        <v>248</v>
+      </c>
+      <c r="BN20" t="n">
+        <v>1768</v>
+      </c>
+      <c r="BO20" t="n">
+        <v>35</v>
+      </c>
+      <c r="BP20" t="n">
+        <v>319</v>
+      </c>
+      <c r="BQ20" t="n">
+        <v>0.8763250883392226</v>
+      </c>
+      <c r="BR20" t="n">
+        <v>0.8471490177287974</v>
+      </c>
+      <c r="BS20" t="n">
+        <v>0.1236749116607774</v>
+      </c>
+      <c r="BT20" t="n">
+        <v>0.1528509822712027</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -4709,6 +5205,30 @@
       <c r="BL21" t="n">
         <v>0.3333333333333333</v>
       </c>
+      <c r="BM21" t="n">
+        <v>213</v>
+      </c>
+      <c r="BN21" t="n">
+        <v>1709</v>
+      </c>
+      <c r="BO21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ21" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR21" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -4907,6 +5427,30 @@
       <c r="BL22" t="n">
         <v>0.3333333333333333</v>
       </c>
+      <c r="BM22" t="n">
+        <v>117</v>
+      </c>
+      <c r="BN22" t="n">
+        <v>1013</v>
+      </c>
+      <c r="BO22" t="n">
+        <v>378</v>
+      </c>
+      <c r="BP22" t="n">
+        <v>2651</v>
+      </c>
+      <c r="BQ22" t="n">
+        <v>0.2363636363636364</v>
+      </c>
+      <c r="BR22" t="n">
+        <v>0.2764737991266376</v>
+      </c>
+      <c r="BS22" t="n">
+        <v>0.7636363636363637</v>
+      </c>
+      <c r="BT22" t="n">
+        <v>0.7235262008733624</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -5105,6 +5649,30 @@
       <c r="BL23" t="n">
         <v>0</v>
       </c>
+      <c r="BM23" t="n">
+        <v>393</v>
+      </c>
+      <c r="BN23" t="n">
+        <v>2866.6</v>
+      </c>
+      <c r="BO23" t="n">
+        <v>192</v>
+      </c>
+      <c r="BP23" t="n">
+        <v>1548.9</v>
+      </c>
+      <c r="BQ23" t="n">
+        <v>0.6717948717948717</v>
+      </c>
+      <c r="BR23" t="n">
+        <v>0.6492129996602876</v>
+      </c>
+      <c r="BS23" t="n">
+        <v>0.3282051282051282</v>
+      </c>
+      <c r="BT23" t="n">
+        <v>0.3507870003397124</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -5303,6 +5871,30 @@
       <c r="BL24" t="n">
         <v>0</v>
       </c>
+      <c r="BM24" t="n">
+        <v>191</v>
+      </c>
+      <c r="BN24" t="n">
+        <v>1384.8</v>
+      </c>
+      <c r="BO24" t="n">
+        <v>213</v>
+      </c>
+      <c r="BP24" t="n">
+        <v>1856.7</v>
+      </c>
+      <c r="BQ24" t="n">
+        <v>0.4727722772277227</v>
+      </c>
+      <c r="BR24" t="n">
+        <v>0.4272096251735308</v>
+      </c>
+      <c r="BS24" t="n">
+        <v>0.5272277227722773</v>
+      </c>
+      <c r="BT24" t="n">
+        <v>0.5727903748264692</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -5501,6 +6093,30 @@
       <c r="BL25" t="n">
         <v>0.1111111111111111</v>
       </c>
+      <c r="BM25" t="n">
+        <v>263</v>
+      </c>
+      <c r="BN25" t="n">
+        <v>2140.6</v>
+      </c>
+      <c r="BO25" t="n">
+        <v>171</v>
+      </c>
+      <c r="BP25" t="n">
+        <v>1363.7</v>
+      </c>
+      <c r="BQ25" t="n">
+        <v>0.6059907834101382</v>
+      </c>
+      <c r="BR25" t="n">
+        <v>0.610849527723083</v>
+      </c>
+      <c r="BS25" t="n">
+        <v>0.3940092165898618</v>
+      </c>
+      <c r="BT25" t="n">
+        <v>0.3891504722769169</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -5699,6 +6315,30 @@
       <c r="BL26" t="n">
         <v>0</v>
       </c>
+      <c r="BM26" t="n">
+        <v>230</v>
+      </c>
+      <c r="BN26" t="n">
+        <v>1914</v>
+      </c>
+      <c r="BO26" t="n">
+        <v>246</v>
+      </c>
+      <c r="BP26" t="n">
+        <v>2044.8</v>
+      </c>
+      <c r="BQ26" t="n">
+        <v>0.4831932773109244</v>
+      </c>
+      <c r="BR26" t="n">
+        <v>0.4834798423764777</v>
+      </c>
+      <c r="BS26" t="n">
+        <v>0.5168067226890757</v>
+      </c>
+      <c r="BT26" t="n">
+        <v>0.5165201576235222</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -5897,6 +6537,30 @@
       <c r="BL27" t="n">
         <v>0</v>
       </c>
+      <c r="BM27" t="n">
+        <v>150</v>
+      </c>
+      <c r="BN27" t="n">
+        <v>1179</v>
+      </c>
+      <c r="BO27" t="n">
+        <v>216</v>
+      </c>
+      <c r="BP27" t="n">
+        <v>1536</v>
+      </c>
+      <c r="BQ27" t="n">
+        <v>0.4098360655737705</v>
+      </c>
+      <c r="BR27" t="n">
+        <v>0.4342541436464089</v>
+      </c>
+      <c r="BS27" t="n">
+        <v>0.5901639344262295</v>
+      </c>
+      <c r="BT27" t="n">
+        <v>0.5657458563535912</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -6095,6 +6759,30 @@
       <c r="BL28" t="n">
         <v>0</v>
       </c>
+      <c r="BM28" t="n">
+        <v>230</v>
+      </c>
+      <c r="BN28" t="n">
+        <v>1693</v>
+      </c>
+      <c r="BO28" t="n">
+        <v>203</v>
+      </c>
+      <c r="BP28" t="n">
+        <v>1418</v>
+      </c>
+      <c r="BQ28" t="n">
+        <v>0.5311778290993071</v>
+      </c>
+      <c r="BR28" t="n">
+        <v>0.5441980070716811</v>
+      </c>
+      <c r="BS28" t="n">
+        <v>0.4688221709006928</v>
+      </c>
+      <c r="BT28" t="n">
+        <v>0.4558019929283189</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -6293,6 +6981,30 @@
       <c r="BL29" t="n">
         <v>0</v>
       </c>
+      <c r="BM29" t="n">
+        <v>79</v>
+      </c>
+      <c r="BN29" t="n">
+        <v>537</v>
+      </c>
+      <c r="BO29" t="n">
+        <v>70</v>
+      </c>
+      <c r="BP29" t="n">
+        <v>422</v>
+      </c>
+      <c r="BQ29" t="n">
+        <v>0.5302013422818792</v>
+      </c>
+      <c r="BR29" t="n">
+        <v>0.5599582898852972</v>
+      </c>
+      <c r="BS29" t="n">
+        <v>0.4697986577181208</v>
+      </c>
+      <c r="BT29" t="n">
+        <v>0.4400417101147028</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -6491,6 +7203,30 @@
       <c r="BL30" t="n">
         <v>0</v>
       </c>
+      <c r="BM30" t="n">
+        <v>41</v>
+      </c>
+      <c r="BN30" t="n">
+        <v>475</v>
+      </c>
+      <c r="BO30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ30" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR30" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT30" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -6689,6 +7425,30 @@
       <c r="BL31" t="n">
         <v>0</v>
       </c>
+      <c r="BM31" t="n">
+        <v>13</v>
+      </c>
+      <c r="BN31" t="n">
+        <v>144</v>
+      </c>
+      <c r="BO31" t="n">
+        <v>17</v>
+      </c>
+      <c r="BP31" t="n">
+        <v>178</v>
+      </c>
+      <c r="BQ31" t="n">
+        <v>0.4333333333333333</v>
+      </c>
+      <c r="BR31" t="n">
+        <v>0.4472049689440994</v>
+      </c>
+      <c r="BS31" t="n">
+        <v>0.5666666666666667</v>
+      </c>
+      <c r="BT31" t="n">
+        <v>0.5527950310559007</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -6887,6 +7647,30 @@
       <c r="BL32" t="n">
         <v>0</v>
       </c>
+      <c r="BM32" t="n">
+        <v>10</v>
+      </c>
+      <c r="BN32" t="n">
+        <v>91</v>
+      </c>
+      <c r="BO32" t="n">
+        <v>12</v>
+      </c>
+      <c r="BP32" t="n">
+        <v>115</v>
+      </c>
+      <c r="BQ32" t="n">
+        <v>0.4545454545454545</v>
+      </c>
+      <c r="BR32" t="n">
+        <v>0.441747572815534</v>
+      </c>
+      <c r="BS32" t="n">
+        <v>0.5454545454545454</v>
+      </c>
+      <c r="BT32" t="n">
+        <v>0.558252427184466</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -7085,6 +7869,30 @@
       <c r="BL33" t="n">
         <v>0</v>
       </c>
+      <c r="BM33" t="n">
+        <v>1</v>
+      </c>
+      <c r="BN33" t="n">
+        <v>9</v>
+      </c>
+      <c r="BO33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ33" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR33" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT33" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -7283,6 +8091,30 @@
       <c r="BL34" t="n">
         <v>0</v>
       </c>
+      <c r="BM34" t="n">
+        <v>1</v>
+      </c>
+      <c r="BN34" t="n">
+        <v>6</v>
+      </c>
+      <c r="BO34" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP34" t="n">
+        <v>10</v>
+      </c>
+      <c r="BQ34" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BR34" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="BS34" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BT34" t="n">
+        <v>0.625</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -7481,6 +8313,30 @@
       <c r="BL35" t="n">
         <v>0</v>
       </c>
+      <c r="BM35" t="n">
+        <v>8</v>
+      </c>
+      <c r="BN35" t="n">
+        <v>80</v>
+      </c>
+      <c r="BO35" t="n">
+        <v>5</v>
+      </c>
+      <c r="BP35" t="n">
+        <v>55</v>
+      </c>
+      <c r="BQ35" t="n">
+        <v>0.6153846153846154</v>
+      </c>
+      <c r="BR35" t="n">
+        <v>0.5925925925925926</v>
+      </c>
+      <c r="BS35" t="n">
+        <v>0.3846153846153846</v>
+      </c>
+      <c r="BT35" t="n">
+        <v>0.4074074074074074</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -7679,6 +8535,30 @@
       <c r="BL36" t="n">
         <v>0</v>
       </c>
+      <c r="BM36" t="n">
+        <v>14</v>
+      </c>
+      <c r="BN36" t="n">
+        <v>73.3</v>
+      </c>
+      <c r="BO36" t="n">
+        <v>39</v>
+      </c>
+      <c r="BP36" t="n">
+        <v>197.5</v>
+      </c>
+      <c r="BQ36" t="n">
+        <v>0.2641509433962264</v>
+      </c>
+      <c r="BR36" t="n">
+        <v>0.2706794682422452</v>
+      </c>
+      <c r="BS36" t="n">
+        <v>0.7358490566037735</v>
+      </c>
+      <c r="BT36" t="n">
+        <v>0.7293205317577548</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -7877,6 +8757,30 @@
       <c r="BL37" t="n">
         <v>0</v>
       </c>
+      <c r="BM37" t="n">
+        <v>91</v>
+      </c>
+      <c r="BN37" t="n">
+        <v>378.5</v>
+      </c>
+      <c r="BO37" t="n">
+        <v>156</v>
+      </c>
+      <c r="BP37" t="n">
+        <v>463</v>
+      </c>
+      <c r="BQ37" t="n">
+        <v>0.3684210526315789</v>
+      </c>
+      <c r="BR37" t="n">
+        <v>0.4497920380273321</v>
+      </c>
+      <c r="BS37" t="n">
+        <v>0.631578947368421</v>
+      </c>
+      <c r="BT37" t="n">
+        <v>0.5502079619726679</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -8075,6 +8979,30 @@
       <c r="BL38" t="n">
         <v>0</v>
       </c>
+      <c r="BM38" t="n">
+        <v>292</v>
+      </c>
+      <c r="BN38" t="n">
+        <v>853</v>
+      </c>
+      <c r="BO38" t="n">
+        <v>46</v>
+      </c>
+      <c r="BP38" t="n">
+        <v>199.1</v>
+      </c>
+      <c r="BQ38" t="n">
+        <v>0.863905325443787</v>
+      </c>
+      <c r="BR38" t="n">
+        <v>0.8107594335139244</v>
+      </c>
+      <c r="BS38" t="n">
+        <v>0.136094674556213</v>
+      </c>
+      <c r="BT38" t="n">
+        <v>0.1892405664860754</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -8273,6 +9201,30 @@
       <c r="BL39" t="n">
         <v>0</v>
       </c>
+      <c r="BM39" t="n">
+        <v>370</v>
+      </c>
+      <c r="BN39" t="n">
+        <v>1173</v>
+      </c>
+      <c r="BO39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ39" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR39" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT39" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -8471,6 +9423,30 @@
       <c r="BL40" t="n">
         <v>0</v>
       </c>
+      <c r="BM40" t="n">
+        <v>90</v>
+      </c>
+      <c r="BN40" t="n">
+        <v>237.1</v>
+      </c>
+      <c r="BO40" t="n">
+        <v>168</v>
+      </c>
+      <c r="BP40" t="n">
+        <v>534.1</v>
+      </c>
+      <c r="BQ40" t="n">
+        <v>0.3488372093023256</v>
+      </c>
+      <c r="BR40" t="n">
+        <v>0.3074429460580912</v>
+      </c>
+      <c r="BS40" t="n">
+        <v>0.6511627906976745</v>
+      </c>
+      <c r="BT40" t="n">
+        <v>0.6925570539419087</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -8669,6 +9645,30 @@
       <c r="BL41" t="n">
         <v>0</v>
       </c>
+      <c r="BM41" t="n">
+        <v>103</v>
+      </c>
+      <c r="BN41" t="n">
+        <v>276.3</v>
+      </c>
+      <c r="BO41" t="n">
+        <v>97</v>
+      </c>
+      <c r="BP41" t="n">
+        <v>320</v>
+      </c>
+      <c r="BQ41" t="n">
+        <v>0.515</v>
+      </c>
+      <c r="BR41" t="n">
+        <v>0.4633573704511152</v>
+      </c>
+      <c r="BS41" t="n">
+        <v>0.485</v>
+      </c>
+      <c r="BT41" t="n">
+        <v>0.5366426295488848</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -8867,6 +9867,30 @@
       <c r="BL42" t="n">
         <v>0</v>
       </c>
+      <c r="BM42" t="n">
+        <v>53</v>
+      </c>
+      <c r="BN42" t="n">
+        <v>127.9</v>
+      </c>
+      <c r="BO42" t="n">
+        <v>48</v>
+      </c>
+      <c r="BP42" t="n">
+        <v>113.3</v>
+      </c>
+      <c r="BQ42" t="n">
+        <v>0.5247524752475248</v>
+      </c>
+      <c r="BR42" t="n">
+        <v>0.5302653399668324</v>
+      </c>
+      <c r="BS42" t="n">
+        <v>0.4752475247524752</v>
+      </c>
+      <c r="BT42" t="n">
+        <v>0.4697346600331675</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -9065,6 +10089,30 @@
       <c r="BL43" t="n">
         <v>0</v>
       </c>
+      <c r="BM43" t="n">
+        <v>62</v>
+      </c>
+      <c r="BN43" t="n">
+        <v>150.8</v>
+      </c>
+      <c r="BO43" t="n">
+        <v>47</v>
+      </c>
+      <c r="BP43" t="n">
+        <v>98.2</v>
+      </c>
+      <c r="BQ43" t="n">
+        <v>0.5688073394495413</v>
+      </c>
+      <c r="BR43" t="n">
+        <v>0.6056224899598394</v>
+      </c>
+      <c r="BS43" t="n">
+        <v>0.4311926605504587</v>
+      </c>
+      <c r="BT43" t="n">
+        <v>0.3943775100401606</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -9263,6 +10311,30 @@
       <c r="BL44" t="n">
         <v>0</v>
       </c>
+      <c r="BM44" t="n">
+        <v>66</v>
+      </c>
+      <c r="BN44" t="n">
+        <v>153.9</v>
+      </c>
+      <c r="BO44" t="n">
+        <v>77</v>
+      </c>
+      <c r="BP44" t="n">
+        <v>191.7</v>
+      </c>
+      <c r="BQ44" t="n">
+        <v>0.4615384615384616</v>
+      </c>
+      <c r="BR44" t="n">
+        <v>0.4453125</v>
+      </c>
+      <c r="BS44" t="n">
+        <v>0.5384615384615384</v>
+      </c>
+      <c r="BT44" t="n">
+        <v>0.5546875</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -9461,6 +10533,30 @@
       <c r="BL45" t="n">
         <v>0</v>
       </c>
+      <c r="BM45" t="n">
+        <v>81</v>
+      </c>
+      <c r="BN45" t="n">
+        <v>196.7</v>
+      </c>
+      <c r="BO45" t="n">
+        <v>29</v>
+      </c>
+      <c r="BP45" t="n">
+        <v>71.60000000000001</v>
+      </c>
+      <c r="BQ45" t="n">
+        <v>0.7363636363636363</v>
+      </c>
+      <c r="BR45" t="n">
+        <v>0.7331345508758852</v>
+      </c>
+      <c r="BS45" t="n">
+        <v>0.2636363636363636</v>
+      </c>
+      <c r="BT45" t="n">
+        <v>0.2668654491241148</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -9659,6 +10755,30 @@
       <c r="BL46" t="n">
         <v>0</v>
       </c>
+      <c r="BM46" t="n">
+        <v>84</v>
+      </c>
+      <c r="BN46" t="n">
+        <v>208.7</v>
+      </c>
+      <c r="BO46" t="n">
+        <v>163</v>
+      </c>
+      <c r="BP46" t="n">
+        <v>403.2</v>
+      </c>
+      <c r="BQ46" t="n">
+        <v>0.340080971659919</v>
+      </c>
+      <c r="BR46" t="n">
+        <v>0.3410688020918451</v>
+      </c>
+      <c r="BS46" t="n">
+        <v>0.659919028340081</v>
+      </c>
+      <c r="BT46" t="n">
+        <v>0.6589311979081549</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -9857,6 +10977,30 @@
       <c r="BL47" t="n">
         <v>0</v>
       </c>
+      <c r="BM47" t="n">
+        <v>147</v>
+      </c>
+      <c r="BN47" t="n">
+        <v>475.2</v>
+      </c>
+      <c r="BO47" t="n">
+        <v>119</v>
+      </c>
+      <c r="BP47" t="n">
+        <v>341.1</v>
+      </c>
+      <c r="BQ47" t="n">
+        <v>0.5526315789473685</v>
+      </c>
+      <c r="BR47" t="n">
+        <v>0.5821389195148842</v>
+      </c>
+      <c r="BS47" t="n">
+        <v>0.4473684210526316</v>
+      </c>
+      <c r="BT47" t="n">
+        <v>0.4178610804851158</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -10055,6 +11199,30 @@
       <c r="BL48" t="n">
         <v>0</v>
       </c>
+      <c r="BM48" t="n">
+        <v>169</v>
+      </c>
+      <c r="BN48" t="n">
+        <v>531.5</v>
+      </c>
+      <c r="BO48" t="n">
+        <v>243</v>
+      </c>
+      <c r="BP48" t="n">
+        <v>812</v>
+      </c>
+      <c r="BQ48" t="n">
+        <v>0.4101941747572815</v>
+      </c>
+      <c r="BR48" t="n">
+        <v>0.3956084852995906</v>
+      </c>
+      <c r="BS48" t="n">
+        <v>0.5898058252427184</v>
+      </c>
+      <c r="BT48" t="n">
+        <v>0.6043915147004094</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -10253,6 +11421,30 @@
       <c r="BL49" t="n">
         <v>0</v>
       </c>
+      <c r="BM49" t="n">
+        <v>189</v>
+      </c>
+      <c r="BN49" t="n">
+        <v>638.8000000000001</v>
+      </c>
+      <c r="BO49" t="n">
+        <v>286</v>
+      </c>
+      <c r="BP49" t="n">
+        <v>982.9</v>
+      </c>
+      <c r="BQ49" t="n">
+        <v>0.3978947368421052</v>
+      </c>
+      <c r="BR49" t="n">
+        <v>0.3939076277979898</v>
+      </c>
+      <c r="BS49" t="n">
+        <v>0.6021052631578947</v>
+      </c>
+      <c r="BT49" t="n">
+        <v>0.6060923722020102</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -10451,6 +11643,30 @@
       <c r="BL50" t="n">
         <v>0</v>
       </c>
+      <c r="BM50" t="n">
+        <v>342</v>
+      </c>
+      <c r="BN50" t="n">
+        <v>1281.3</v>
+      </c>
+      <c r="BO50" t="n">
+        <v>109</v>
+      </c>
+      <c r="BP50" t="n">
+        <v>409.3</v>
+      </c>
+      <c r="BQ50" t="n">
+        <v>0.7583148558758315</v>
+      </c>
+      <c r="BR50" t="n">
+        <v>0.757896604755708</v>
+      </c>
+      <c r="BS50" t="n">
+        <v>0.2416851441241685</v>
+      </c>
+      <c r="BT50" t="n">
+        <v>0.2421033952442919</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -10649,6 +11865,30 @@
       <c r="BL51" t="n">
         <v>0</v>
       </c>
+      <c r="BM51" t="n">
+        <v>481</v>
+      </c>
+      <c r="BN51" t="n">
+        <v>1792.8</v>
+      </c>
+      <c r="BO51" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP51" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ51" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR51" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS51" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT51" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -10847,6 +12087,30 @@
       <c r="BL52" t="n">
         <v>0</v>
       </c>
+      <c r="BM52" t="n">
+        <v>147</v>
+      </c>
+      <c r="BN52" t="n">
+        <v>412.2</v>
+      </c>
+      <c r="BO52" t="n">
+        <v>268</v>
+      </c>
+      <c r="BP52" t="n">
+        <v>1094.4</v>
+      </c>
+      <c r="BQ52" t="n">
+        <v>0.3542168674698795</v>
+      </c>
+      <c r="BR52" t="n">
+        <v>0.2735961768219832</v>
+      </c>
+      <c r="BS52" t="n">
+        <v>0.6457831325301204</v>
+      </c>
+      <c r="BT52" t="n">
+        <v>0.7264038231780168</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -11045,6 +12309,30 @@
       <c r="BL53" t="n">
         <v>0</v>
       </c>
+      <c r="BM53" t="n">
+        <v>170</v>
+      </c>
+      <c r="BN53" t="n">
+        <v>513.4</v>
+      </c>
+      <c r="BO53" t="n">
+        <v>149</v>
+      </c>
+      <c r="BP53" t="n">
+        <v>482.6</v>
+      </c>
+      <c r="BQ53" t="n">
+        <v>0.5329153605015674</v>
+      </c>
+      <c r="BR53" t="n">
+        <v>0.5154618473895582</v>
+      </c>
+      <c r="BS53" t="n">
+        <v>0.4670846394984326</v>
+      </c>
+      <c r="BT53" t="n">
+        <v>0.4845381526104418</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -11243,6 +12531,30 @@
       <c r="BL54" t="n">
         <v>0</v>
       </c>
+      <c r="BM54" t="n">
+        <v>96</v>
+      </c>
+      <c r="BN54" t="n">
+        <v>297.6</v>
+      </c>
+      <c r="BO54" t="n">
+        <v>106</v>
+      </c>
+      <c r="BP54" t="n">
+        <v>253.5</v>
+      </c>
+      <c r="BQ54" t="n">
+        <v>0.4752475247524752</v>
+      </c>
+      <c r="BR54" t="n">
+        <v>0.5400108873162766</v>
+      </c>
+      <c r="BS54" t="n">
+        <v>0.5247524752475248</v>
+      </c>
+      <c r="BT54" t="n">
+        <v>0.4599891126837234</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -11441,6 +12753,30 @@
       <c r="BL55" t="n">
         <v>0</v>
       </c>
+      <c r="BM55" t="n">
+        <v>85</v>
+      </c>
+      <c r="BN55" t="n">
+        <v>241.6</v>
+      </c>
+      <c r="BO55" t="n">
+        <v>78</v>
+      </c>
+      <c r="BP55" t="n">
+        <v>226.3</v>
+      </c>
+      <c r="BQ55" t="n">
+        <v>0.5214723926380368</v>
+      </c>
+      <c r="BR55" t="n">
+        <v>0.5163496473605471</v>
+      </c>
+      <c r="BS55" t="n">
+        <v>0.4785276073619632</v>
+      </c>
+      <c r="BT55" t="n">
+        <v>0.4836503526394529</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -11639,6 +12975,30 @@
       <c r="BL56" t="n">
         <v>0</v>
       </c>
+      <c r="BM56" t="n">
+        <v>59</v>
+      </c>
+      <c r="BN56" t="n">
+        <v>180.9</v>
+      </c>
+      <c r="BO56" t="n">
+        <v>53</v>
+      </c>
+      <c r="BP56" t="n">
+        <v>180</v>
+      </c>
+      <c r="BQ56" t="n">
+        <v>0.5267857142857143</v>
+      </c>
+      <c r="BR56" t="n">
+        <v>0.5012468827930174</v>
+      </c>
+      <c r="BS56" t="n">
+        <v>0.4732142857142857</v>
+      </c>
+      <c r="BT56" t="n">
+        <v>0.4987531172069825</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -11837,6 +13197,30 @@
       <c r="BL57" t="n">
         <v>0</v>
       </c>
+      <c r="BM57" t="n">
+        <v>49</v>
+      </c>
+      <c r="BN57" t="n">
+        <v>125.2</v>
+      </c>
+      <c r="BO57" t="n">
+        <v>40</v>
+      </c>
+      <c r="BP57" t="n">
+        <v>105</v>
+      </c>
+      <c r="BQ57" t="n">
+        <v>0.550561797752809</v>
+      </c>
+      <c r="BR57" t="n">
+        <v>0.5438748913987836</v>
+      </c>
+      <c r="BS57" t="n">
+        <v>0.449438202247191</v>
+      </c>
+      <c r="BT57" t="n">
+        <v>0.4561251086012163</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -12035,6 +13419,30 @@
       <c r="BL58" t="n">
         <v>0</v>
       </c>
+      <c r="BM58" t="n">
+        <v>75</v>
+      </c>
+      <c r="BN58" t="n">
+        <v>245.8</v>
+      </c>
+      <c r="BO58" t="n">
+        <v>125</v>
+      </c>
+      <c r="BP58" t="n">
+        <v>403.9</v>
+      </c>
+      <c r="BQ58" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="BR58" t="n">
+        <v>0.3783284592889026</v>
+      </c>
+      <c r="BS58" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="BT58" t="n">
+        <v>0.6216715407110974</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -12233,6 +13641,30 @@
       <c r="BL59" t="n">
         <v>0</v>
       </c>
+      <c r="BM59" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN59" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO59" t="n">
+        <v>26</v>
+      </c>
+      <c r="BP59" t="n">
+        <v>100.4</v>
+      </c>
+      <c r="BQ59" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR59" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS59" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT59" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -12431,6 +13863,30 @@
       <c r="BL60" t="n">
         <v>0</v>
       </c>
+      <c r="BM60" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN60" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO60" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP60" t="n">
+        <v>3</v>
+      </c>
+      <c r="BQ60" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR60" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS60" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT60" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -12629,6 +14085,30 @@
       <c r="BL61" t="n">
         <v>0</v>
       </c>
+      <c r="BM61" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN61" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO61" t="n">
+        <v>335</v>
+      </c>
+      <c r="BP61" t="n">
+        <v>3682.5</v>
+      </c>
+      <c r="BQ61" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR61" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS61" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT61" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -12827,6 +14307,30 @@
       <c r="BL62" t="n">
         <v>0.5</v>
       </c>
+      <c r="BM62" t="n">
+        <v>382</v>
+      </c>
+      <c r="BN62" t="n">
+        <v>2825.67</v>
+      </c>
+      <c r="BO62" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP62" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ62" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR62" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS62" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT62" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -13025,6 +14529,30 @@
       <c r="BL63" t="n">
         <v>0</v>
       </c>
+      <c r="BM63" t="n">
+        <v>285</v>
+      </c>
+      <c r="BN63" t="n">
+        <v>1342.2</v>
+      </c>
+      <c r="BO63" t="n">
+        <v>80</v>
+      </c>
+      <c r="BP63" t="n">
+        <v>376.3</v>
+      </c>
+      <c r="BQ63" t="n">
+        <v>0.7808219178082192</v>
+      </c>
+      <c r="BR63" t="n">
+        <v>0.7810299679953449</v>
+      </c>
+      <c r="BS63" t="n">
+        <v>0.2191780821917808</v>
+      </c>
+      <c r="BT63" t="n">
+        <v>0.2189700320046552</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -13223,6 +14751,30 @@
       <c r="BL64" t="n">
         <v>0</v>
       </c>
+      <c r="BM64" t="n">
+        <v>1665</v>
+      </c>
+      <c r="BN64" t="n">
+        <v>7476</v>
+      </c>
+      <c r="BO64" t="n">
+        <v>1262</v>
+      </c>
+      <c r="BP64" t="n">
+        <v>5814</v>
+      </c>
+      <c r="BQ64" t="n">
+        <v>0.5688418175606423</v>
+      </c>
+      <c r="BR64" t="n">
+        <v>0.562528216704289</v>
+      </c>
+      <c r="BS64" t="n">
+        <v>0.4311581824393577</v>
+      </c>
+      <c r="BT64" t="n">
+        <v>0.4374717832957111</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -13421,6 +14973,30 @@
       <c r="BL65" t="n">
         <v>0</v>
       </c>
+      <c r="BM65" t="n">
+        <v>1062</v>
+      </c>
+      <c r="BN65" t="n">
+        <v>4924.6</v>
+      </c>
+      <c r="BO65" t="n">
+        <v>1426</v>
+      </c>
+      <c r="BP65" t="n">
+        <v>6950.2</v>
+      </c>
+      <c r="BQ65" t="n">
+        <v>0.4268488745980707</v>
+      </c>
+      <c r="BR65" t="n">
+        <v>0.4147101424866104</v>
+      </c>
+      <c r="BS65" t="n">
+        <v>0.5731511254019293</v>
+      </c>
+      <c r="BT65" t="n">
+        <v>0.5852898575133897</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -13619,6 +15195,30 @@
       <c r="BL66" t="n">
         <v>0</v>
       </c>
+      <c r="BM66" t="n">
+        <v>1952</v>
+      </c>
+      <c r="BN66" t="n">
+        <v>8685.700000000001</v>
+      </c>
+      <c r="BO66" t="n">
+        <v>1182</v>
+      </c>
+      <c r="BP66" t="n">
+        <v>5427.3</v>
+      </c>
+      <c r="BQ66" t="n">
+        <v>0.6228462029355456</v>
+      </c>
+      <c r="BR66" t="n">
+        <v>0.6154396655565791</v>
+      </c>
+      <c r="BS66" t="n">
+        <v>0.3771537970644544</v>
+      </c>
+      <c r="BT66" t="n">
+        <v>0.384560334443421</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -13817,6 +15417,30 @@
       <c r="BL67" t="n">
         <v>0</v>
       </c>
+      <c r="BM67" t="n">
+        <v>885</v>
+      </c>
+      <c r="BN67" t="n">
+        <v>4084</v>
+      </c>
+      <c r="BO67" t="n">
+        <v>1472</v>
+      </c>
+      <c r="BP67" t="n">
+        <v>6805.6</v>
+      </c>
+      <c r="BQ67" t="n">
+        <v>0.3754773016546457</v>
+      </c>
+      <c r="BR67" t="n">
+        <v>0.3750367322950338</v>
+      </c>
+      <c r="BS67" t="n">
+        <v>0.6245226983453542</v>
+      </c>
+      <c r="BT67" t="n">
+        <v>0.6249632677049662</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -14015,6 +15639,30 @@
       <c r="BL68" t="n">
         <v>0</v>
       </c>
+      <c r="BM68" t="n">
+        <v>1186</v>
+      </c>
+      <c r="BN68" t="n">
+        <v>5673.7</v>
+      </c>
+      <c r="BO68" t="n">
+        <v>1383</v>
+      </c>
+      <c r="BP68" t="n">
+        <v>6728.9</v>
+      </c>
+      <c r="BQ68" t="n">
+        <v>0.461658232775399</v>
+      </c>
+      <c r="BR68" t="n">
+        <v>0.4574605324689984</v>
+      </c>
+      <c r="BS68" t="n">
+        <v>0.538341767224601</v>
+      </c>
+      <c r="BT68" t="n">
+        <v>0.5425394675310016</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -14213,6 +15861,30 @@
       <c r="BL69" t="n">
         <v>0</v>
       </c>
+      <c r="BM69" t="n">
+        <v>1515</v>
+      </c>
+      <c r="BN69" t="n">
+        <v>7218.4</v>
+      </c>
+      <c r="BO69" t="n">
+        <v>1275</v>
+      </c>
+      <c r="BP69" t="n">
+        <v>6199.6</v>
+      </c>
+      <c r="BQ69" t="n">
+        <v>0.543010752688172</v>
+      </c>
+      <c r="BR69" t="n">
+        <v>0.5379639290505291</v>
+      </c>
+      <c r="BS69" t="n">
+        <v>0.4569892473118279</v>
+      </c>
+      <c r="BT69" t="n">
+        <v>0.4620360709494709</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -14411,6 +16083,30 @@
       <c r="BL70" t="n">
         <v>0</v>
       </c>
+      <c r="BM70" t="n">
+        <v>1690</v>
+      </c>
+      <c r="BN70" t="n">
+        <v>7738.3</v>
+      </c>
+      <c r="BO70" t="n">
+        <v>1428</v>
+      </c>
+      <c r="BP70" t="n">
+        <v>7116.7</v>
+      </c>
+      <c r="BQ70" t="n">
+        <v>0.5420141116100065</v>
+      </c>
+      <c r="BR70" t="n">
+        <v>0.5209222484012117</v>
+      </c>
+      <c r="BS70" t="n">
+        <v>0.4579858883899936</v>
+      </c>
+      <c r="BT70" t="n">
+        <v>0.4790777515987883</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -14609,6 +16305,30 @@
       <c r="BL71" t="n">
         <v>0</v>
       </c>
+      <c r="BM71" t="n">
+        <v>1441</v>
+      </c>
+      <c r="BN71" t="n">
+        <v>6760.6</v>
+      </c>
+      <c r="BO71" t="n">
+        <v>1818</v>
+      </c>
+      <c r="BP71" t="n">
+        <v>8519.6</v>
+      </c>
+      <c r="BQ71" t="n">
+        <v>0.4421601718318502</v>
+      </c>
+      <c r="BR71" t="n">
+        <v>0.4424418528553291</v>
+      </c>
+      <c r="BS71" t="n">
+        <v>0.5578398281681497</v>
+      </c>
+      <c r="BT71" t="n">
+        <v>0.5575581471446709</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -14807,6 +16527,30 @@
       <c r="BL72" t="n">
         <v>0</v>
       </c>
+      <c r="BM72" t="n">
+        <v>1194</v>
+      </c>
+      <c r="BN72" t="n">
+        <v>5379.4</v>
+      </c>
+      <c r="BO72" t="n">
+        <v>2418</v>
+      </c>
+      <c r="BP72" t="n">
+        <v>11979.5</v>
+      </c>
+      <c r="BQ72" t="n">
+        <v>0.3305647840531561</v>
+      </c>
+      <c r="BR72" t="n">
+        <v>0.3098929079607579</v>
+      </c>
+      <c r="BS72" t="n">
+        <v>0.6694352159468439</v>
+      </c>
+      <c r="BT72" t="n">
+        <v>0.690107092039242</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -15005,6 +16749,30 @@
       <c r="BL73" t="n">
         <v>0</v>
       </c>
+      <c r="BM73" t="n">
+        <v>3891</v>
+      </c>
+      <c r="BN73" t="n">
+        <v>19355.9</v>
+      </c>
+      <c r="BO73" t="n">
+        <v>624</v>
+      </c>
+      <c r="BP73" t="n">
+        <v>4030.1</v>
+      </c>
+      <c r="BQ73" t="n">
+        <v>0.8617940199335549</v>
+      </c>
+      <c r="BR73" t="n">
+        <v>0.827670401094672</v>
+      </c>
+      <c r="BS73" t="n">
+        <v>0.1382059800664452</v>
+      </c>
+      <c r="BT73" t="n">
+        <v>0.172329598905328</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -15203,6 +16971,30 @@
       <c r="BL74" t="n">
         <v>0</v>
       </c>
+      <c r="BM74" t="n">
+        <v>3837</v>
+      </c>
+      <c r="BN74" t="n">
+        <v>17853.9</v>
+      </c>
+      <c r="BO74" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP74" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ74" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR74" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS74" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT74" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -15401,6 +17193,30 @@
       <c r="BL75" t="n">
         <v>0</v>
       </c>
+      <c r="BM75" t="n">
+        <v>766</v>
+      </c>
+      <c r="BN75" t="n">
+        <v>3853.5</v>
+      </c>
+      <c r="BO75" t="n">
+        <v>2100</v>
+      </c>
+      <c r="BP75" t="n">
+        <v>9996.6</v>
+      </c>
+      <c r="BQ75" t="n">
+        <v>0.267271458478716</v>
+      </c>
+      <c r="BR75" t="n">
+        <v>0.2782290380574869</v>
+      </c>
+      <c r="BS75" t="n">
+        <v>0.732728541521284</v>
+      </c>
+      <c r="BT75" t="n">
+        <v>0.7217709619425131</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -15599,6 +17415,30 @@
       <c r="BL76" t="n">
         <v>0</v>
       </c>
+      <c r="BM76" t="n">
+        <v>1863</v>
+      </c>
+      <c r="BN76" t="n">
+        <v>8329</v>
+      </c>
+      <c r="BO76" t="n">
+        <v>1309</v>
+      </c>
+      <c r="BP76" t="n">
+        <v>6182.5</v>
+      </c>
+      <c r="BQ76" t="n">
+        <v>0.5873266078184111</v>
+      </c>
+      <c r="BR76" t="n">
+        <v>0.5739585845708576</v>
+      </c>
+      <c r="BS76" t="n">
+        <v>0.4126733921815889</v>
+      </c>
+      <c r="BT76" t="n">
+        <v>0.4260414154291424</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -15797,6 +17637,30 @@
       <c r="BL77" t="n">
         <v>0</v>
       </c>
+      <c r="BM77" t="n">
+        <v>927</v>
+      </c>
+      <c r="BN77" t="n">
+        <v>4233</v>
+      </c>
+      <c r="BO77" t="n">
+        <v>1683</v>
+      </c>
+      <c r="BP77" t="n">
+        <v>7752.9</v>
+      </c>
+      <c r="BQ77" t="n">
+        <v>0.3551724137931034</v>
+      </c>
+      <c r="BR77" t="n">
+        <v>0.3531649688383851</v>
+      </c>
+      <c r="BS77" t="n">
+        <v>0.6448275862068965</v>
+      </c>
+      <c r="BT77" t="n">
+        <v>0.6468350311616149</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -15995,6 +17859,30 @@
       <c r="BL78" t="n">
         <v>0</v>
       </c>
+      <c r="BM78" t="n">
+        <v>1890</v>
+      </c>
+      <c r="BN78" t="n">
+        <v>8573.1</v>
+      </c>
+      <c r="BO78" t="n">
+        <v>1261</v>
+      </c>
+      <c r="BP78" t="n">
+        <v>5860.7</v>
+      </c>
+      <c r="BQ78" t="n">
+        <v>0.5998095842589654</v>
+      </c>
+      <c r="BR78" t="n">
+        <v>0.5939600105308374</v>
+      </c>
+      <c r="BS78" t="n">
+        <v>0.4001904157410346</v>
+      </c>
+      <c r="BT78" t="n">
+        <v>0.4060399894691626</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -16193,6 +18081,30 @@
       <c r="BL79" t="n">
         <v>0</v>
       </c>
+      <c r="BM79" t="n">
+        <v>1030</v>
+      </c>
+      <c r="BN79" t="n">
+        <v>4564.6</v>
+      </c>
+      <c r="BO79" t="n">
+        <v>1551</v>
+      </c>
+      <c r="BP79" t="n">
+        <v>6950.6</v>
+      </c>
+      <c r="BQ79" t="n">
+        <v>0.3990701278574196</v>
+      </c>
+      <c r="BR79" t="n">
+        <v>0.3963978046408226</v>
+      </c>
+      <c r="BS79" t="n">
+        <v>0.6009298721425804</v>
+      </c>
+      <c r="BT79" t="n">
+        <v>0.6036021953591775</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -16391,6 +18303,30 @@
       <c r="BL80" t="n">
         <v>0</v>
       </c>
+      <c r="BM80" t="n">
+        <v>997</v>
+      </c>
+      <c r="BN80" t="n">
+        <v>4255.1</v>
+      </c>
+      <c r="BO80" t="n">
+        <v>1589</v>
+      </c>
+      <c r="BP80" t="n">
+        <v>7052.9</v>
+      </c>
+      <c r="BQ80" t="n">
+        <v>0.38553750966744</v>
+      </c>
+      <c r="BR80" t="n">
+        <v>0.3762911213300318</v>
+      </c>
+      <c r="BS80" t="n">
+        <v>0.61446249033256</v>
+      </c>
+      <c r="BT80" t="n">
+        <v>0.6237088786699682</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -16589,6 +18525,30 @@
       <c r="BL81" t="n">
         <v>0</v>
       </c>
+      <c r="BM81" t="n">
+        <v>1101</v>
+      </c>
+      <c r="BN81" t="n">
+        <v>4786</v>
+      </c>
+      <c r="BO81" t="n">
+        <v>1591</v>
+      </c>
+      <c r="BP81" t="n">
+        <v>6948</v>
+      </c>
+      <c r="BQ81" t="n">
+        <v>0.4089895988112927</v>
+      </c>
+      <c r="BR81" t="n">
+        <v>0.4078745525822396</v>
+      </c>
+      <c r="BS81" t="n">
+        <v>0.5910104011887073</v>
+      </c>
+      <c r="BT81" t="n">
+        <v>0.5921254474177604</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -16787,6 +18747,30 @@
       <c r="BL82" t="n">
         <v>0</v>
       </c>
+      <c r="BM82" t="n">
+        <v>390</v>
+      </c>
+      <c r="BN82" t="n">
+        <v>1728.9</v>
+      </c>
+      <c r="BO82" t="n">
+        <v>397</v>
+      </c>
+      <c r="BP82" t="n">
+        <v>1787.4</v>
+      </c>
+      <c r="BQ82" t="n">
+        <v>0.4955527318932655</v>
+      </c>
+      <c r="BR82" t="n">
+        <v>0.4916815971333504</v>
+      </c>
+      <c r="BS82" t="n">
+        <v>0.5044472681067345</v>
+      </c>
+      <c r="BT82" t="n">
+        <v>0.5083184028666496</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -16985,6 +18969,30 @@
       <c r="BL83" t="n">
         <v>0.04</v>
       </c>
+      <c r="BM83" t="n">
+        <v>13</v>
+      </c>
+      <c r="BN83" t="n">
+        <v>262</v>
+      </c>
+      <c r="BO83" t="n">
+        <v>44</v>
+      </c>
+      <c r="BP83" t="n">
+        <v>391</v>
+      </c>
+      <c r="BQ83" t="n">
+        <v>0.2280701754385965</v>
+      </c>
+      <c r="BR83" t="n">
+        <v>0.4012251148545176</v>
+      </c>
+      <c r="BS83" t="n">
+        <v>0.7719298245614035</v>
+      </c>
+      <c r="BT83" t="n">
+        <v>0.5987748851454824</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -17183,6 +19191,30 @@
       <c r="BL84" t="n">
         <v>0.2</v>
       </c>
+      <c r="BM84" t="n">
+        <v>68</v>
+      </c>
+      <c r="BN84" t="n">
+        <v>793</v>
+      </c>
+      <c r="BO84" t="n">
+        <v>12</v>
+      </c>
+      <c r="BP84" t="n">
+        <v>106.5</v>
+      </c>
+      <c r="BQ84" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="BR84" t="n">
+        <v>0.8816008893829905</v>
+      </c>
+      <c r="BS84" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="BT84" t="n">
+        <v>0.1183991106170094</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -17381,6 +19413,30 @@
       <c r="BL85" t="n">
         <v>0.1481481481481481</v>
       </c>
+      <c r="BM85" t="n">
+        <v>46</v>
+      </c>
+      <c r="BN85" t="n">
+        <v>497.4</v>
+      </c>
+      <c r="BO85" t="n">
+        <v>64</v>
+      </c>
+      <c r="BP85" t="n">
+        <v>883</v>
+      </c>
+      <c r="BQ85" t="n">
+        <v>0.4181818181818182</v>
+      </c>
+      <c r="BR85" t="n">
+        <v>0.3603303390321645</v>
+      </c>
+      <c r="BS85" t="n">
+        <v>0.5818181818181818</v>
+      </c>
+      <c r="BT85" t="n">
+        <v>0.6396696609678354</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -17579,6 +19635,30 @@
       <c r="BL86" t="n">
         <v>0.04</v>
       </c>
+      <c r="BM86" t="n">
+        <v>53</v>
+      </c>
+      <c r="BN86" t="n">
+        <v>479</v>
+      </c>
+      <c r="BO86" t="n">
+        <v>56</v>
+      </c>
+      <c r="BP86" t="n">
+        <v>494.8</v>
+      </c>
+      <c r="BQ86" t="n">
+        <v>0.4862385321100918</v>
+      </c>
+      <c r="BR86" t="n">
+        <v>0.4918874512220169</v>
+      </c>
+      <c r="BS86" t="n">
+        <v>0.5137614678899083</v>
+      </c>
+      <c r="BT86" t="n">
+        <v>0.5081125487779832</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -17777,6 +19857,30 @@
       <c r="BL87" t="n">
         <v>0.2012903225806452</v>
       </c>
+      <c r="BM87" t="n">
+        <v>133</v>
+      </c>
+      <c r="BN87" t="n">
+        <v>1152.4</v>
+      </c>
+      <c r="BO87" t="n">
+        <v>15</v>
+      </c>
+      <c r="BP87" t="n">
+        <v>149</v>
+      </c>
+      <c r="BQ87" t="n">
+        <v>0.8986486486486487</v>
+      </c>
+      <c r="BR87" t="n">
+        <v>0.8855079145535577</v>
+      </c>
+      <c r="BS87" t="n">
+        <v>0.1013513513513514</v>
+      </c>
+      <c r="BT87" t="n">
+        <v>0.1144920854464423</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -17975,6 +20079,30 @@
       <c r="BL88" t="n">
         <v>0.1289473684210526</v>
       </c>
+      <c r="BM88" t="n">
+        <v>188</v>
+      </c>
+      <c r="BN88" t="n">
+        <v>1770.4</v>
+      </c>
+      <c r="BO88" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP88" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ88" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR88" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS88" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT88" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -18173,6 +20301,30 @@
       <c r="BL89" t="n">
         <v>0.2140804597701149</v>
       </c>
+      <c r="BM89" t="n">
+        <v>45</v>
+      </c>
+      <c r="BN89" t="n">
+        <v>716.5</v>
+      </c>
+      <c r="BO89" t="n">
+        <v>57</v>
+      </c>
+      <c r="BP89" t="n">
+        <v>838.9</v>
+      </c>
+      <c r="BQ89" t="n">
+        <v>0.4411764705882353</v>
+      </c>
+      <c r="BR89" t="n">
+        <v>0.4606532081779606</v>
+      </c>
+      <c r="BS89" t="n">
+        <v>0.5588235294117647</v>
+      </c>
+      <c r="BT89" t="n">
+        <v>0.5393467918220393</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -18371,6 +20523,30 @@
       <c r="BL90" t="n">
         <v>0.2222222222222222</v>
       </c>
+      <c r="BM90" t="n">
+        <v>53</v>
+      </c>
+      <c r="BN90" t="n">
+        <v>478.3</v>
+      </c>
+      <c r="BO90" t="n">
+        <v>20</v>
+      </c>
+      <c r="BP90" t="n">
+        <v>311.4</v>
+      </c>
+      <c r="BQ90" t="n">
+        <v>0.726027397260274</v>
+      </c>
+      <c r="BR90" t="n">
+        <v>0.6056730403950867</v>
+      </c>
+      <c r="BS90" t="n">
+        <v>0.273972602739726</v>
+      </c>
+      <c r="BT90" t="n">
+        <v>0.3943269596049132</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -18569,6 +20745,30 @@
       <c r="BL91" t="n">
         <v>0.05263157894736842</v>
       </c>
+      <c r="BM91" t="n">
+        <v>48</v>
+      </c>
+      <c r="BN91" t="n">
+        <v>944</v>
+      </c>
+      <c r="BO91" t="n">
+        <v>24</v>
+      </c>
+      <c r="BP91" t="n">
+        <v>357.8</v>
+      </c>
+      <c r="BQ91" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="BR91" t="n">
+        <v>0.7251497925948687</v>
+      </c>
+      <c r="BS91" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="BT91" t="n">
+        <v>0.2748502074051314</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -18767,6 +20967,30 @@
       <c r="BL92" t="n">
         <v>0.1475279106858054</v>
       </c>
+      <c r="BM92" t="n">
+        <v>164</v>
+      </c>
+      <c r="BN92" t="n">
+        <v>1500</v>
+      </c>
+      <c r="BO92" t="n">
+        <v>53</v>
+      </c>
+      <c r="BP92" t="n">
+        <v>324</v>
+      </c>
+      <c r="BQ92" t="n">
+        <v>0.7557603686635944</v>
+      </c>
+      <c r="BR92" t="n">
+        <v>0.8223684210526315</v>
+      </c>
+      <c r="BS92" t="n">
+        <v>0.2442396313364055</v>
+      </c>
+      <c r="BT92" t="n">
+        <v>0.1776315789473684</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -18965,6 +21189,30 @@
       <c r="BL93" t="n">
         <v>0.06477732793522267</v>
       </c>
+      <c r="BM93" t="n">
+        <v>129</v>
+      </c>
+      <c r="BN93" t="n">
+        <v>1174.35</v>
+      </c>
+      <c r="BO93" t="n">
+        <v>95</v>
+      </c>
+      <c r="BP93" t="n">
+        <v>844.6</v>
+      </c>
+      <c r="BQ93" t="n">
+        <v>0.5758928571428571</v>
+      </c>
+      <c r="BR93" t="n">
+        <v>0.5816637361004482</v>
+      </c>
+      <c r="BS93" t="n">
+        <v>0.4241071428571428</v>
+      </c>
+      <c r="BT93" t="n">
+        <v>0.4183362638995518</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -19163,6 +21411,30 @@
       <c r="BL94" t="n">
         <v>0.02564102564102564</v>
       </c>
+      <c r="BM94" t="n">
+        <v>228</v>
+      </c>
+      <c r="BN94" t="n">
+        <v>1671.5</v>
+      </c>
+      <c r="BO94" t="n">
+        <v>108</v>
+      </c>
+      <c r="BP94" t="n">
+        <v>737.15</v>
+      </c>
+      <c r="BQ94" t="n">
+        <v>0.6785714285714286</v>
+      </c>
+      <c r="BR94" t="n">
+        <v>0.6939571959396342</v>
+      </c>
+      <c r="BS94" t="n">
+        <v>0.3214285714285715</v>
+      </c>
+      <c r="BT94" t="n">
+        <v>0.3060428040603658</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -19361,6 +21633,30 @@
       <c r="BL95" t="n">
         <v>0.03448275862068965</v>
       </c>
+      <c r="BM95" t="n">
+        <v>109</v>
+      </c>
+      <c r="BN95" t="n">
+        <v>822.65</v>
+      </c>
+      <c r="BO95" t="n">
+        <v>92</v>
+      </c>
+      <c r="BP95" t="n">
+        <v>549.1</v>
+      </c>
+      <c r="BQ95" t="n">
+        <v>0.5422885572139303</v>
+      </c>
+      <c r="BR95" t="n">
+        <v>0.5997084016766904</v>
+      </c>
+      <c r="BS95" t="n">
+        <v>0.4577114427860697</v>
+      </c>
+      <c r="BT95" t="n">
+        <v>0.4002915983233097</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -19559,6 +21855,30 @@
       <c r="BL96" t="n">
         <v>0</v>
       </c>
+      <c r="BM96" t="n">
+        <v>59</v>
+      </c>
+      <c r="BN96" t="n">
+        <v>483.8</v>
+      </c>
+      <c r="BO96" t="n">
+        <v>32</v>
+      </c>
+      <c r="BP96" t="n">
+        <v>254.35</v>
+      </c>
+      <c r="BQ96" t="n">
+        <v>0.6483516483516484</v>
+      </c>
+      <c r="BR96" t="n">
+        <v>0.655422339632866</v>
+      </c>
+      <c r="BS96" t="n">
+        <v>0.3516483516483517</v>
+      </c>
+      <c r="BT96" t="n">
+        <v>0.3445776603671341</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -19757,6 +22077,30 @@
       <c r="BL97" t="n">
         <v>0</v>
       </c>
+      <c r="BM97" t="n">
+        <v>28</v>
+      </c>
+      <c r="BN97" t="n">
+        <v>284.25</v>
+      </c>
+      <c r="BO97" t="n">
+        <v>35</v>
+      </c>
+      <c r="BP97" t="n">
+        <v>311.95</v>
+      </c>
+      <c r="BQ97" t="n">
+        <v>0.4444444444444444</v>
+      </c>
+      <c r="BR97" t="n">
+        <v>0.4767695404226769</v>
+      </c>
+      <c r="BS97" t="n">
+        <v>0.5555555555555556</v>
+      </c>
+      <c r="BT97" t="n">
+        <v>0.5232304595773229</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -19955,6 +22299,30 @@
       <c r="BL98" t="n">
         <v>0.0303030303030303</v>
       </c>
+      <c r="BM98" t="n">
+        <v>56</v>
+      </c>
+      <c r="BN98" t="n">
+        <v>609.25</v>
+      </c>
+      <c r="BO98" t="n">
+        <v>88</v>
+      </c>
+      <c r="BP98" t="n">
+        <v>574.3</v>
+      </c>
+      <c r="BQ98" t="n">
+        <v>0.3888888888888889</v>
+      </c>
+      <c r="BR98" t="n">
+        <v>0.5147649022010055</v>
+      </c>
+      <c r="BS98" t="n">
+        <v>0.6111111111111112</v>
+      </c>
+      <c r="BT98" t="n">
+        <v>0.4852350977989945</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -20153,6 +22521,30 @@
       <c r="BL99" t="n">
         <v>0</v>
       </c>
+      <c r="BM99" t="n">
+        <v>245</v>
+      </c>
+      <c r="BN99" t="n">
+        <v>1681.9</v>
+      </c>
+      <c r="BO99" t="n">
+        <v>23</v>
+      </c>
+      <c r="BP99" t="n">
+        <v>153.3</v>
+      </c>
+      <c r="BQ99" t="n">
+        <v>0.914179104477612</v>
+      </c>
+      <c r="BR99" t="n">
+        <v>0.9164668700959023</v>
+      </c>
+      <c r="BS99" t="n">
+        <v>0.08582089552238806</v>
+      </c>
+      <c r="BT99" t="n">
+        <v>0.08353312990409766</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -20351,6 +22743,30 @@
       <c r="BL100" t="n">
         <v>0.02272727272727273</v>
       </c>
+      <c r="BM100" t="n">
+        <v>356</v>
+      </c>
+      <c r="BN100" t="n">
+        <v>2873.55</v>
+      </c>
+      <c r="BO100" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP100" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ100" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR100" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS100" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT100" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -20549,6 +22965,30 @@
       <c r="BL101" t="n">
         <v>0.03846153846153846</v>
       </c>
+      <c r="BM101" t="n">
+        <v>44</v>
+      </c>
+      <c r="BN101" t="n">
+        <v>441.3</v>
+      </c>
+      <c r="BO101" t="n">
+        <v>120</v>
+      </c>
+      <c r="BP101" t="n">
+        <v>779.5</v>
+      </c>
+      <c r="BQ101" t="n">
+        <v>0.2682926829268293</v>
+      </c>
+      <c r="BR101" t="n">
+        <v>0.3614842726081258</v>
+      </c>
+      <c r="BS101" t="n">
+        <v>0.7317073170731707</v>
+      </c>
+      <c r="BT101" t="n">
+        <v>0.6385157273918742</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -20747,6 +23187,30 @@
       <c r="BL102" t="n">
         <v>0.05263157894736842</v>
       </c>
+      <c r="BM102" t="n">
+        <v>39</v>
+      </c>
+      <c r="BN102" t="n">
+        <v>293.2</v>
+      </c>
+      <c r="BO102" t="n">
+        <v>31</v>
+      </c>
+      <c r="BP102" t="n">
+        <v>165.45</v>
+      </c>
+      <c r="BQ102" t="n">
+        <v>0.5571428571428572</v>
+      </c>
+      <c r="BR102" t="n">
+        <v>0.6392674152403793</v>
+      </c>
+      <c r="BS102" t="n">
+        <v>0.4428571428571428</v>
+      </c>
+      <c r="BT102" t="n">
+        <v>0.3607325847596206</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -20945,6 +23409,30 @@
       <c r="BL103" t="n">
         <v>0.03703703703703703</v>
       </c>
+      <c r="BM103" t="n">
+        <v>81</v>
+      </c>
+      <c r="BN103" t="n">
+        <v>576.85</v>
+      </c>
+      <c r="BO103" t="n">
+        <v>77</v>
+      </c>
+      <c r="BP103" t="n">
+        <v>625</v>
+      </c>
+      <c r="BQ103" t="n">
+        <v>0.5126582278481012</v>
+      </c>
+      <c r="BR103" t="n">
+        <v>0.4799683820776304</v>
+      </c>
+      <c r="BS103" t="n">
+        <v>0.4873417721518987</v>
+      </c>
+      <c r="BT103" t="n">
+        <v>0.5200316179223697</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -21143,6 +23631,30 @@
       <c r="BL104" t="n">
         <v>0.08333333333333333</v>
       </c>
+      <c r="BM104" t="n">
+        <v>287</v>
+      </c>
+      <c r="BN104" t="n">
+        <v>2072.5</v>
+      </c>
+      <c r="BO104" t="n">
+        <v>161</v>
+      </c>
+      <c r="BP104" t="n">
+        <v>1262</v>
+      </c>
+      <c r="BQ104" t="n">
+        <v>0.640625</v>
+      </c>
+      <c r="BR104" t="n">
+        <v>0.6215324636377269</v>
+      </c>
+      <c r="BS104" t="n">
+        <v>0.359375</v>
+      </c>
+      <c r="BT104" t="n">
+        <v>0.3784675363622732</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -21341,6 +23853,30 @@
       <c r="BL105" t="n">
         <v>0.1008771929824561</v>
       </c>
+      <c r="BM105" t="n">
+        <v>238</v>
+      </c>
+      <c r="BN105" t="n">
+        <v>1424.5</v>
+      </c>
+      <c r="BO105" t="n">
+        <v>322</v>
+      </c>
+      <c r="BP105" t="n">
+        <v>2313.35</v>
+      </c>
+      <c r="BQ105" t="n">
+        <v>0.425</v>
+      </c>
+      <c r="BR105" t="n">
+        <v>0.3811014353170941</v>
+      </c>
+      <c r="BS105" t="n">
+        <v>0.575</v>
+      </c>
+      <c r="BT105" t="n">
+        <v>0.6188985646829059</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -21539,6 +24075,30 @@
       <c r="BL106" t="n">
         <v>0.1121856866537718</v>
       </c>
+      <c r="BM106" t="n">
+        <v>288</v>
+      </c>
+      <c r="BN106" t="n">
+        <v>2091.95</v>
+      </c>
+      <c r="BO106" t="n">
+        <v>148</v>
+      </c>
+      <c r="BP106" t="n">
+        <v>1189.65</v>
+      </c>
+      <c r="BQ106" t="n">
+        <v>0.6605504587155964</v>
+      </c>
+      <c r="BR106" t="n">
+        <v>0.6374786689419795</v>
+      </c>
+      <c r="BS106" t="n">
+        <v>0.3394495412844037</v>
+      </c>
+      <c r="BT106" t="n">
+        <v>0.3625213310580205</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -21737,6 +24297,30 @@
       <c r="BL107" t="n">
         <v>0.1141649048625793</v>
       </c>
+      <c r="BM107" t="n">
+        <v>114</v>
+      </c>
+      <c r="BN107" t="n">
+        <v>693.5</v>
+      </c>
+      <c r="BO107" t="n">
+        <v>165</v>
+      </c>
+      <c r="BP107" t="n">
+        <v>1272.8</v>
+      </c>
+      <c r="BQ107" t="n">
+        <v>0.4086021505376344</v>
+      </c>
+      <c r="BR107" t="n">
+        <v>0.3526928749427859</v>
+      </c>
+      <c r="BS107" t="n">
+        <v>0.5913978494623656</v>
+      </c>
+      <c r="BT107" t="n">
+        <v>0.647307125057214</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -21935,6 +24519,30 @@
       <c r="BL108" t="n">
         <v>0</v>
       </c>
+      <c r="BM108" t="n">
+        <v>29</v>
+      </c>
+      <c r="BN108" t="n">
+        <v>160.3</v>
+      </c>
+      <c r="BO108" t="n">
+        <v>3</v>
+      </c>
+      <c r="BP108" t="n">
+        <v>17</v>
+      </c>
+      <c r="BQ108" t="n">
+        <v>0.90625</v>
+      </c>
+      <c r="BR108" t="n">
+        <v>0.904117315284828</v>
+      </c>
+      <c r="BS108" t="n">
+        <v>0.09375</v>
+      </c>
+      <c r="BT108" t="n">
+        <v>0.09588268471517201</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -22133,6 +24741,30 @@
       <c r="BL109" t="n">
         <v>0</v>
       </c>
+      <c r="BM109" t="n">
+        <v>110</v>
+      </c>
+      <c r="BN109" t="n">
+        <v>444</v>
+      </c>
+      <c r="BO109" t="n">
+        <v>39</v>
+      </c>
+      <c r="BP109" t="n">
+        <v>114.5</v>
+      </c>
+      <c r="BQ109" t="n">
+        <v>0.738255033557047</v>
+      </c>
+      <c r="BR109" t="n">
+        <v>0.7949865711727843</v>
+      </c>
+      <c r="BS109" t="n">
+        <v>0.261744966442953</v>
+      </c>
+      <c r="BT109" t="n">
+        <v>0.2050134288272158</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -22331,6 +24963,30 @@
       <c r="BL110" t="n">
         <v>0</v>
       </c>
+      <c r="BM110" t="n">
+        <v>89</v>
+      </c>
+      <c r="BN110" t="n">
+        <v>333.5</v>
+      </c>
+      <c r="BO110" t="n">
+        <v>163</v>
+      </c>
+      <c r="BP110" t="n">
+        <v>610</v>
+      </c>
+      <c r="BQ110" t="n">
+        <v>0.3531746031746032</v>
+      </c>
+      <c r="BR110" t="n">
+        <v>0.3534711181770006</v>
+      </c>
+      <c r="BS110" t="n">
+        <v>0.6468253968253969</v>
+      </c>
+      <c r="BT110" t="n">
+        <v>0.6465288818229995</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -22529,6 +25185,30 @@
       <c r="BL111" t="n">
         <v>0</v>
       </c>
+      <c r="BM111" t="n">
+        <v>227</v>
+      </c>
+      <c r="BN111" t="n">
+        <v>862.5</v>
+      </c>
+      <c r="BO111" t="n">
+        <v>156</v>
+      </c>
+      <c r="BP111" t="n">
+        <v>473</v>
+      </c>
+      <c r="BQ111" t="n">
+        <v>0.5926892950391645</v>
+      </c>
+      <c r="BR111" t="n">
+        <v>0.6458255335080494</v>
+      </c>
+      <c r="BS111" t="n">
+        <v>0.4073107049608355</v>
+      </c>
+      <c r="BT111" t="n">
+        <v>0.3541744664919506</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -22727,6 +25407,30 @@
       <c r="BL112" t="n">
         <v>0</v>
       </c>
+      <c r="BM112" t="n">
+        <v>85</v>
+      </c>
+      <c r="BN112" t="n">
+        <v>284</v>
+      </c>
+      <c r="BO112" t="n">
+        <v>119</v>
+      </c>
+      <c r="BP112" t="n">
+        <v>339</v>
+      </c>
+      <c r="BQ112" t="n">
+        <v>0.4166666666666667</v>
+      </c>
+      <c r="BR112" t="n">
+        <v>0.4558587479935794</v>
+      </c>
+      <c r="BS112" t="n">
+        <v>0.5833333333333334</v>
+      </c>
+      <c r="BT112" t="n">
+        <v>0.5441412520064205</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -22925,6 +25629,30 @@
       <c r="BL113" t="n">
         <v>0</v>
       </c>
+      <c r="BM113" t="n">
+        <v>106</v>
+      </c>
+      <c r="BN113" t="n">
+        <v>446</v>
+      </c>
+      <c r="BO113" t="n">
+        <v>90</v>
+      </c>
+      <c r="BP113" t="n">
+        <v>299</v>
+      </c>
+      <c r="BQ113" t="n">
+        <v>0.5408163265306123</v>
+      </c>
+      <c r="BR113" t="n">
+        <v>0.5986577181208054</v>
+      </c>
+      <c r="BS113" t="n">
+        <v>0.4591836734693878</v>
+      </c>
+      <c r="BT113" t="n">
+        <v>0.4013422818791946</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -23123,6 +25851,30 @@
       <c r="BL114" t="n">
         <v>0</v>
       </c>
+      <c r="BM114" t="n">
+        <v>98</v>
+      </c>
+      <c r="BN114" t="n">
+        <v>351.5</v>
+      </c>
+      <c r="BO114" t="n">
+        <v>166</v>
+      </c>
+      <c r="BP114" t="n">
+        <v>548.5</v>
+      </c>
+      <c r="BQ114" t="n">
+        <v>0.3712121212121212</v>
+      </c>
+      <c r="BR114" t="n">
+        <v>0.3905555555555555</v>
+      </c>
+      <c r="BS114" t="n">
+        <v>0.6287878787878788</v>
+      </c>
+      <c r="BT114" t="n">
+        <v>0.6094444444444445</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -23321,6 +26073,30 @@
       <c r="BL115" t="n">
         <v>0</v>
       </c>
+      <c r="BM115" t="n">
+        <v>181</v>
+      </c>
+      <c r="BN115" t="n">
+        <v>684.5</v>
+      </c>
+      <c r="BO115" t="n">
+        <v>112</v>
+      </c>
+      <c r="BP115" t="n">
+        <v>393.5</v>
+      </c>
+      <c r="BQ115" t="n">
+        <v>0.6177474402730375</v>
+      </c>
+      <c r="BR115" t="n">
+        <v>0.6349721706864564</v>
+      </c>
+      <c r="BS115" t="n">
+        <v>0.3822525597269625</v>
+      </c>
+      <c r="BT115" t="n">
+        <v>0.3650278293135436</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -23519,6 +26295,30 @@
       <c r="BL116" t="n">
         <v>0</v>
       </c>
+      <c r="BM116" t="n">
+        <v>103</v>
+      </c>
+      <c r="BN116" t="n">
+        <v>309</v>
+      </c>
+      <c r="BO116" t="n">
+        <v>110</v>
+      </c>
+      <c r="BP116" t="n">
+        <v>345</v>
+      </c>
+      <c r="BQ116" t="n">
+        <v>0.4835680751173709</v>
+      </c>
+      <c r="BR116" t="n">
+        <v>0.4724770642201835</v>
+      </c>
+      <c r="BS116" t="n">
+        <v>0.5164319248826291</v>
+      </c>
+      <c r="BT116" t="n">
+        <v>0.5275229357798165</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -23717,6 +26517,30 @@
       <c r="BL117" t="n">
         <v>0</v>
       </c>
+      <c r="BM117" t="n">
+        <v>198</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>592</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>282</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>1117</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>0.4125</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.3464014043300175</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>0.5875</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.6535985956699825</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -23915,6 +26739,30 @@
       <c r="BL118" t="n">
         <v>0</v>
       </c>
+      <c r="BM118" t="n">
+        <v>399</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>1400.5</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -24113,6 +26961,30 @@
       <c r="BL119" t="n">
         <v>0</v>
       </c>
+      <c r="BM119" t="n">
+        <v>536</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>1723.5</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -24311,6 +27183,30 @@
       <c r="BL120" t="n">
         <v>0</v>
       </c>
+      <c r="BM120" t="n">
+        <v>69</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>231.5</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>137</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>404.5</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>0.3349514563106796</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.3639937106918239</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.6650485436893204</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.6360062893081762</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -24509,6 +27405,30 @@
       <c r="BL121" t="n">
         <v>0</v>
       </c>
+      <c r="BM121" t="n">
+        <v>147</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>469</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>159</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>514</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.4803921568627451</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.4771108850457783</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.5196078431372549</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.5228891149542217</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -24707,6 +27627,30 @@
       <c r="BL122" t="n">
         <v>0</v>
       </c>
+      <c r="BM122" t="n">
+        <v>132</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>445</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>215</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>729</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>0.3804034582132565</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>0.379045996592845</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.6195965417867435</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.620954003407155</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -24905,6 +27849,30 @@
       <c r="BL123" t="n">
         <v>0</v>
       </c>
+      <c r="BM123" t="n">
+        <v>338</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>1171.5</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>261</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>857</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.5642737896494157</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.5775203352230712</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.4357262103505843</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.4224796647769288</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -25103,6 +28071,30 @@
       <c r="BL124" t="n">
         <v>0</v>
       </c>
+      <c r="BM124" t="n">
+        <v>155</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>612</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>154</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>485.5</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.5016181229773463</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.5576309794988611</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.4983818770226537</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.442369020501139</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -25301,6 +28293,30 @@
       <c r="BL125" t="n">
         <v>0</v>
       </c>
+      <c r="BM125" t="n">
+        <v>5</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>21</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>63.5</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.1923076923076923</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.1753246753246753</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.8076923076923077</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.8246753246753247</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -25499,6 +28515,30 @@
       <c r="BL126" t="n">
         <v>0</v>
       </c>
+      <c r="BM126" t="n">
+        <v>66</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>207</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>120</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>354.5</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.3548387096774194</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.3686553873552983</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.6451612903225806</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.6313446126447017</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -25696,6 +28736,30 @@
       </c>
       <c r="BL127" t="n">
         <v>0</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>49</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>158.5</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>54</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>210.5</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.4757281553398058</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.4295392953929539</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.5242718446601942</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.5704607046070461</v>
       </c>
     </row>
   </sheetData>
